--- a/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10016788,10016792,10016790,10048480,10016791,10016793,10016788,10016792,10016790,10048480,10016791,10016793,10016788,10016792,10016790,10048480,10016791,10016793,10016788,10016792,10016790,10016785,10016791,10016793,10016788,10016792,10016790,10016785,10016791,10016793,10016788,10016792,10016790,10016785,10016791,10016793,10016788,10016792,10016790,10016785,10016791,10016793,10016788,10016792,10016790,10048481,10016794,10016793,10016788,10016792,10016790,10048481,10016794,10016793,10016788,10016792,10016790,10048481,10016794,10016793,10016788,10016792,10016790,10048481,10016794,10016793,10016788,10016792,10016790,10016786,10016794,10016793,10016788,10016792,10016790,10016786,10016794,10016793,10016788,10016792,10016790,10016786,10016794,10016793,10016788,10016792,10016790,10016787,10016794,10016793,10016788,10016792,10016790,10016787,10016795,10016788,10016792,10016790,10016787,10016795,10016788,10016792,10016790,10016787,10016795,10016788,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016792,10016792,10016792,10016792</t>
+          <t>10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016787,10016790,10016787,10016794,10016793,10016788,10016787,10016790,10016787,10016795,10016788,10016787,10016790,10016787,10016795,10016788,10016787,10016790,10016787,10016795,10016788,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016792,10016792,10016792,10016792</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L2 W21/25; N=152; EHP=15595.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x18,fast:30x18,medium:83x7,swarm:84x42,heavy:88x15,medium:108x8,medium:123x7</t>
+          <t>L2 W21/25; N=152; EHP=25041.438124; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x18,heavy:88x15,medium:83x7,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10016799,10016803,10016801,10048482,10016802,10016804,10016799,10016803,10016801,10048482,10016802,10016804,10016799,10016803,10016801,10048482,10016802,10016804,10016799,10016803,10016801,10048482,10016802,10016804,10016799,10016803,10016801,10016796,10016802,10016804,10016799,10016803,10016801,10016796,10016802,10016804,10016799,10016803,10016801,10016796,10016802,10016804,10016799,10016803,10016801,10048483,10016802,10016804,10016799,10016803,10016801,10048483,10016805,10016804,10016799,10016803,10016801,10048483,10016805,10016804,10016799,10016803,10016801,10048483,10016805,10016804,10016799,10016803,10016801,10016797,10016805,10016804,10016799,10016803,10016801,10016797,10016805,10016804,10016799,10016803,10016801,10016797,10016805,10016804,10016799,10016803,10016801,10016797,10016805,10016804,10016799,10016803,10016801,10016798,10016806,10016799,10016803,10016801,10016798,10016806,10016799,10016803,10016801,10016798,10016806,10016799,10016803,10016798,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016803,10016803,10016803,10016803</t>
+          <t>10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10048483,10016801,10048483,10016802,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016798,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016803,10016803,10016803,10016803</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L2 W22/25; N=158; EHP=15907.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x18,medium:83x8,swarm:84x44,heavy:88x15,medium:108x7,medium:123x8</t>
+          <t>L2 W22/25; N=158; EHP=25548.287686; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x18,heavy:88x15,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10016810,10016814,10016812,10048484,10016813,10016815,10016810,10016814,10016812,10048484,10016813,10016815,10016810,10016814,10016812,10048484,10016813,10016815,10016810,10016814,10016812,10048484,10016813,10016815,10016810,10016814,10016812,10016807,10016813,10016815,10016810,10016814,10016812,10016807,10016813,10016815,10016810,10016814,10016812,10016807,10016813,10016815,10016810,10016814,10016812,10016807,10016813,10016815,10016810,10016814,10016812,10048485,10016816,10016815,10016810,10016814,10016812,10048485,10016816,10016815,10016810,10016814,10016812,10048485,10016816,10016815,10016810,10016814,10016812,10048485,10016816,10016815,10016810,10016814,10016812,10016808,10016816,10016815,10016810,10016814,10016812,10016808,10016816,10016815,10016810,10016814,10016812,10016808,10016816,10016815,10016810,10016814,10016812,10016808,10016816,10016815,10016810,10016814,10016812,10016809,10016817,10016810,10016814,10016812,10016809,10016817,10016810,10016814,10016812,10016809,10016817,10016810,10016814,10016809,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016814,10016814,10016814,10016814</t>
+          <t>10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016809,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016814,10016814,10016814,10016814</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L2 W23/25; N=164; EHP=16226.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x19,medium:83x8,swarm:84x45,heavy:88x16,medium:108x8,medium:123x8</t>
+          <t>L2 W23/25; N=164; EHP=26063.722104; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x19,heavy:88x16,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10016821,10016825,10016823,10048486,10016824,10016826,10016821,10016825,10016823,10048486,10016824,10016826,10016821,10016825,10016823,10048486,10016824,10016826,10016821,10016825,10016823,10048486,10016824,10016826,10016821,10016825,10016823,10016818,10016824,10016826,10016821,10016825,10016823,10016818,10016824,10016826,10016821,10016825,10016823,10016818,10016824,10016826,10016821,10016825,10016823,10016818,10016824,10016826,10016821,10016825,10016823,10048487,10016827,10016826,10016821,10016825,10016823,10048487,10016827,10016826,10016821,10016825,10016823,10048487,10016827,10016826,10016821,10016825,10016823,10048487,10016827,10016826,10016821,10016825,10016823,10016819,10016827,10016826,10016821,10016825,10016823,10016819,10016827,10016826,10016821,10016825,10016823,10016819,10016827,10016826,10016821,10016825,10016823,10016819,10016827,10016826,10016821,10016825,10016823,10016820,10016827,10016826,10016821,10016825,10016823,10016820,10016828,10016821,10016825,10016823,10016820,10016828,10016821,10016825,10016823,10016820,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016825,10016825,10016825,10016825,10016825</t>
+          <t>10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016820,10016823,10016820,10016827,10016826,10016821,10016820,10016823,10016820,10016828,10016821,10016820,10016823,10016820,10016828,10016821,10016820,10016823,10016820,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016825,10016825,10016825,10016825,10016825</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L2 W24/25; N=170; EHP=17375.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x20,medium:83x8,swarm:84x47,heavy:88x17,medium:108x9,medium:123x8</t>
+          <t>L2 W24/25; N=170; EHP=27896.490207; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x20,heavy:88x17,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10016832,10016836,10016834,10048488,10016835,10016837,10016839,10016832,10016836,10016834,10048488,10016835,10016837,10016832,10016836,10016834,10048488,10016835,10016837,10016832,10016836,10016834,10048488,10016835,10016837,10016832,10016836,10016834,10016829,10016835,10016837,10016832,10016836,10016834,10016829,10016835,10016837,10016832,10016836,10016834,10016829,10016835,10016837,10016832,10016836,10016834,10016829,10016835,10016837,10016832,10016836,10016834,10048489,10016835,10016837,10016832,10016836,10016834,10048489,10016838,10016837,10016832,10016836,10016834,10048489,10016838,10016837,10016832,10016836,10016834,10048489,10016838,10016837,10016832,10016836,10016834,10016830,10016838,10016837,10016832,10016836,10016834,10016830,10016838,10016837,10016832,10016836,10016834,10016830,10016838,10016837,10016832,10016836,10016834,10016830,10016838,10016837,10016832,10016836,10016834,10016830,10016838,10016837,10016832,10016836,10016834,10016831,10016840,10016832,10016836,10016834,10016831,10016840,10016832,10016836,10016834,10016831,10016840,10016832,10016836,10016834,10016831,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836</t>
+          <t>10016832,10048488,10016834,10048488,10016835,10016837,10016839,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10048489,10016834,10048489,10016835,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L2 W25/25; N=176; EHP=34688.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x20,fast:30x21,medium:83x9,swarm:84x49,heavy:88x17,medium:108x8,elite:123x1,medium:123x9</t>
+          <t>L2 W25/25; N=176; EHP=55692.679138; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x21,heavy:88x17,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L2 W1/25; N=32; EHP=177.408000; normal:17x16,normal:18x16</t>
+          <t>L2 W1/25; N=32; EHP=281.663449; normal:17x16,normal:18x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L2 W2/25; N=38; EHP=220.594651; normal:17x19,normal:18x19</t>
+          <t>L2 W2/25; N=38; EHP=350.229135; normal:17x19,normal:18x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3144136,3144673,3144019,3144136,3144673,3144091,3144136,3144673,3144099,3144136,3144673,3144107,3144136,3144673,3144115,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144136,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144</t>
+          <t>3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144136,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144136,3144136,3144136,3144136,3144136</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L2 W3/25; N=44; EHP=282.575462; air:2x1,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x14,normal:18x13,swarm:84x12</t>
+          <t>L2 W3/25; N=44; EHP=481.932928; normal:17x19,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3146136,3146673,3146019,3146136,3146673,3146019,3146136,3146673,3146091,3146136,3146673,3146099,3146136,3146673,3146107,3146136,3146673,3146115,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144</t>
+          <t>3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146136,3146136,3146136,3146136,3146136,3146136</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L2 W4/25; N=50; EHP=369.757080; air:2x2,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x15,normal:18x15,swarm:84x14</t>
+          <t>L2 W4/25; N=50; EHP=633.394156; normal:17x21,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3148136,3148673,3148019,3148668,3148136,3148673,3148091,3148668,3148136,3148673,3148091,3148668,3148136,3148673,3148099,3148668,3148136,3148673,3148107,3148988,3148136,3148673,3148107,3148988,3148136,3148673,3148115,3148988,3148136,3148673,3148988,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148144,3148673,3148144,3148673,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144</t>
+          <t>3148136,3148019,3148019,3148668,3148136,3148091,3148091,3148668,3148136,3148091,3148091,3148668,3148136,3148099,3148099,3148668,3148136,3148107,3148107,3148988,3148136,3148107,3148107,3148988,3148136,3148115,3148115,3148988,3148136,3148673,3148988,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148144,3148673,3148144,3148673,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L2 W5/25; N=56; EHP=713.277380; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x13,normal:18x13,medium:83x4,swarm:84x15,medium:123x4</t>
+          <t>L2 W5/25; N=56; EHP=1147.540637; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x4,medium:123x4,normal:17x13,normal:18x13,swarm:84x8 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3150136,3150673,3150019,3150668,3150136,3150673,3150091,3150668,3150136,3150673,3150091,3150668,3150136,3150673,3150099,3150668,3150136,3150673,3150107,3150668,3150136,3150673,3150115,3150988,3150136,3150673,3150115,3150988,3150136,3150673,3150988,3150136,3150673,3150988,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150144,3150673,3150144,3150673,3150144,3150673,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144</t>
+          <t>3150136,3150019,3150019,3150668,3150136,3150091,3150091,3150668,3150136,3150091,3150091,3150668,3150136,3150099,3150099,3150668,3150136,3150107,3150107,3150668,3150136,3150115,3150115,3150988,3150136,3150115,3150115,3150988,3150136,3150673,3150988,3150136,3150673,3150988,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150144,3150673,3150144,3150673,3150144,3150673,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L2 W6/25; N=62; EHP=728.000000; air:2x1,air:11x2,air:12x1,air:13x1,air:14x2,normal:17x14,normal:18x15,medium:83x5,swarm:84x17,medium:123x4</t>
+          <t>L2 W6/25; N=62; EHP=1169.646199; air:2x2,air:11x4,air:12x2,air:13x2,air:14x4,medium:83x5,medium:123x4,normal:17x14,normal:18x15,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3152136,3152673,3152019,3152668,3152136,3152673,3152019,3152668,3152136,3152673,3152091,3152668,3152136,3152673,3152099,3152668,3152136,3152673,3152099,3152668,3152136,3152673,3152107,3152988,3152136,3152673,3152115,3152988,3152136,3152673,3152115,3152988,3152136,3152673,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152673,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144</t>
+          <t>3152136,3152019,3152019,3152668,3152136,3152019,3152019,3152668,3152136,3152091,3152091,3152668,3152136,3152099,3152099,3152668,3152136,3152099,3152099,3152668,3152136,3152107,3152107,3152988,3152136,3152115,3152115,3152988,3152136,3152115,3152115,3152988,3152136,3152673,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152673,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L2 W7/25; N=68; EHP=846.573235; air:2x2,air:11x1,air:12x2,air:13x1,air:14x2,normal:17x16,normal:18x15,medium:83x5,swarm:84x19,medium:123x5</t>
+          <t>L2 W7/25; N=68; EHP=1360.883823; air:2x4,air:11x2,air:12x4,air:13x2,air:14x4,medium:83x5,medium:123x5,normal:17x16,normal:18x15,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3154136,3154673,3154019,3154668,3154136,3154673,3154019,3154668,3154136,3154673,3154091,3154668,3154136,3154673,3154091,3154668,3154136,3154673,3154099,3154668,3154136,3154673,3154099,3154668,3154136,3154673,3154107,3154988,3154136,3154673,3154107,3154988,3154136,3154673,3154115,3154988,3154136,3154673,3154988,3154136,3154673,3154988,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154144,3154673,3154144,3154673,3154144,3154673,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144</t>
+          <t>3154136,3154019,3154019,3154668,3154136,3154019,3154019,3154668,3154136,3154091,3154091,3154668,3154136,3154091,3154091,3154668,3154136,3154099,3154099,3154668,3154136,3154099,3154099,3154668,3154136,3154107,3154107,3154988,3154136,3154107,3154107,3154988,3154136,3154115,3154115,3154988,3154136,3154673,3154988,3154136,3154673,3154988,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154144,3154673,3154144,3154673,3154144,3154673,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L2 W8/25; N=74; EHP=1098.624542; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x17,normal:18x17,medium:83x6,swarm:84x20,medium:123x5</t>
+          <t>L2 W8/25; N=74; EHP=1766.747741; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,medium:83x6,medium:123x5,normal:17x17,normal:18x17,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3156136,3156673,3156019,3156668,3156136,3156673,3156019,3156668,3156136,3156673,3156091,3156668,3156136,3156673,3156091,3156668,3156136,3156673,3156099,3156668,3156136,3156673,3156099,3156668,3156136,3156673,3156107,3156988,3156136,3156673,3156107,3156988,3156136,3156673,3156115,3156988,3156136,3156673,3156115,3156988,3156136,3156673,3156988,3156136,3156673,3156988,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144</t>
+          <t>3156136,3156019,3156019,3156668,3156136,3156019,3156019,3156668,3156136,3156091,3156091,3156668,3156136,3156091,3156091,3156668,3156136,3156099,3156099,3156668,3156136,3156099,3156099,3156668,3156136,3156107,3156107,3156988,3156136,3156107,3156107,3156988,3156136,3156115,3156115,3156988,3156136,3156115,3156115,3156988,3156136,3156673,3156988,3156136,3156673,3156988,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L2 W9/25; N=80; EHP=1407.909888; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x18,medium:83x6,swarm:84x22,medium:123x6</t>
+          <t>L2 W9/25; N=80; EHP=2265.005618; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x6,medium:123x6,normal:17x18,normal:18x18,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3158136,3158673,3158019,3158668,3158136,3158673,3158019,3158668,3158136,3158673,3158091,3158668,3158136,3158673,3158091,3158668,3158136,3158673,3158099,3158668,3158136,3158673,3158099,3158668,3158136,3158673,3158107,3158988,3158136,3158673,3158107,3158988,3158136,3158673,3158115,3158988,3158136,3158673,3158115,3158988,3158136,3158673,3158988,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144</t>
+          <t>3158136,3158019,3158019,3158668,3158136,3158019,3158019,3158668,3158136,3158091,3158091,3158668,3158136,3158091,3158091,3158668,3158136,3158099,3158099,3158668,3158136,3158099,3158099,3158668,3158136,3158107,3158107,3158988,3158136,3158107,3158107,3158988,3158136,3158115,3158115,3158988,3158136,3158115,3158115,3158988,3158136,3158673,3158988,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L2 W10/25; N=86; EHP=2601.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x20,normal:18x20,medium:83x6,swarm:84x24,medium:123x6</t>
+          <t>L2 W10/25; N=86; EHP=4180.799826; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x6,medium:123x6,normal:17x20,normal:18x20,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3160136,3160673,3160242,3160019,3160668,3160709,3160136,3160673,3160242,3160019,3160668,3160709,3160136,3160673,3160242,3160091,3160668,3160709,3160136,3160673,3160242,3160091,3160668,3160709,3160136,3160673,3160242,3160091,3160668,3160709,3160136,3160673,3160242,3160099,3160668,3160709,3160136,3160673,3160242,3160099,3160988,3160709,3160136,3160673,3160242,3160107,3160988,3160709,3160136,3160673,3160242,3160107,3160988,3160709,3160136,3160673,3160242,3160115,3160988,3160136,3160673,3160242,3160115,3160988,3160136,3160673,3160988,3160144,3160673,3160988,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160673</t>
+          <t>3160136,3160019,3160242,3160019,3160668,3160709,3160136,3160019,3160242,3160019,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160099,3160242,3160099,3160668,3160709,3160136,3160099,3160242,3160099,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160709,3160136,3160115,3160242,3160115,3160988,3160136,3160115,3160242,3160115,3160988,3160136,3160673,3160988,3160144,3160673,3160988,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160673</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L2 W11/25; N=92; EHP=2654.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x12,normal:18x11,fast:30x11,medium:83x6,swarm:84x25,heavy:88x9,medium:123x7</t>
+          <t>L2 W11/25; N=92; EHP=4262.207193; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x11,heavy:88x9,medium:83x6,medium:123x7,normal:17x12,normal:18x11,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3162136,3162673,3162242,3162019,3162668,3162709,3162136,3162673,3162242,3162019,3162668,3162709,3162136,3162673,3162242,3162091,3162668,3162709,3162136,3162673,3162242,3162091,3162668,3162709,3162136,3162673,3162242,3162099,3162668,3162709,3162136,3162673,3162242,3162099,3162668,3162709,3162136,3162673,3162242,3162099,3162668,3162709,3162136,3162673,3162242,3162107,3162988,3162709,3162136,3162673,3162242,3162107,3162988,3162709,3162136,3162673,3162242,3162115,3162988,3162136,3162673,3162242,3162115,3162988,3162136,3162673,3162115,3162988,3162144,3162673,3162988,3162144,3162673,3162988,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162673</t>
+          <t>3162136,3162019,3162242,3162019,3162668,3162709,3162136,3162019,3162242,3162019,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162107,3162242,3162107,3162988,3162709,3162136,3162107,3162242,3162107,3162988,3162709,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162115,3162988,3162144,3162673,3162988,3162144,3162673,3162988,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162673</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L2 W12/25; N=98; EHP=2748.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x12,normal:18x13,fast:30x11,medium:83x7,swarm:84x27,heavy:88x9,medium:123x7</t>
+          <t>L2 W12/25; N=98; EHP=4414.775238; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x11,heavy:88x9,medium:83x7,medium:123x7,normal:17x12,normal:18x13,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3164136,3164673,3164242,3164019,3164668,3164709,3164136,3164673,3164242,3164019,3164668,3164709,3164136,3164673,3164242,3164019,3164668,3164709,3164136,3164673,3164242,3164091,3164668,3164709,3164136,3164673,3164242,3164091,3164668,3164709,3164136,3164673,3164242,3164099,3164668,3164709,3164136,3164673,3164242,3164099,3164668,3164709,3164136,3164673,3164242,3164099,3164988,3164709,3164136,3164673,3164242,3164107,3164988,3164709,3164136,3164673,3164242,3164107,3164988,3164709,3164136,3164673,3164242,3164115,3164988,3164136,3164673,3164242,3164115,3164988,3164136,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164673,3164673</t>
+          <t>3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164136,3164099,3164242,3164099,3164988,3164709,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164115,3164242,3164115,3164988,3164136,3164115,3164242,3164115,3164988,3164136,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164673,3164673</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L2 W13/25; N=104; EHP=3353.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x13,normal:18x13,fast:30x12,medium:83x7,swarm:84x29,heavy:88x10,medium:123x8</t>
+          <t>L2 W13/25; N=104; EHP=5382.597937; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x12,heavy:88x10,medium:83x7,medium:123x8,normal:17x13,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3166136,3166673,3166242,3166019,3166668,3166709,3166136,3166673,3166242,3166019,3166668,3166709,3166136,3166673,3166242,3166019,3166668,3166709,3166136,3166673,3166242,3166091,3166668,3166709,3166136,3166673,3166242,3166091,3166668,3166709,3166136,3166673,3166242,3166091,3166668,3166709,3166136,3166673,3166242,3166099,3166668,3166709,3166136,3166673,3166242,3166099,3166668,3166709,3166136,3166673,3166242,3166107,3166988,3166709,3166136,3166673,3166242,3166107,3166988,3166709,3166136,3166673,3166242,3166107,3166988,3166709,3166136,3166673,3166242,3166115,3166988,3166136,3166673,3166242,3166115,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166673,3166673,3166673</t>
+          <t>3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166099,3166242,3166099,3166668,3166709,3166136,3166099,3166242,3166099,3166668,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166115,3166242,3166115,3166988,3166136,3166115,3166242,3166115,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166673,3166673,3166673</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L2 W14/25; N=110; EHP=4049.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x13,normal:18x14,fast:30x13,medium:83x8,swarm:84x30,heavy:88x11,medium:123x8</t>
+          <t>L2 W14/25; N=110; EHP=6501.228076; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x13,heavy:88x11,medium:83x8,medium:123x8,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3168136,3168673,3168242,3168019,3168668,3168709,3168136,3168673,3168242,3168019,3168668,3168709,3168136,3168673,3168242,3168091,3168668,3168709,3168136,3168673,3168242,3168091,3168668,3168709,3168136,3168673,3168242,3168091,3168668,3168709,3168136,3168673,3168242,3168099,3168668,3168709,3168136,3168673,3168242,3168099,3168868,3168709,3168136,3168673,3168242,3168099,3168868,3168709,3168136,3168673,3168242,3168107,3168868,3168709,3168136,3168673,3168242,3168107,3168868,3168709,3168136,3168673,3168242,3168107,3168868,3168709,3168136,3168673,3168242,3168115,3168868,3168136,3168673,3168242,3168115,3168988,3168136,3168673,3168115,3168988,3168136,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168673,3168673</t>
+          <t>3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168099,3168242,3168099,3168668,3168709,3168136,3168099,3168242,3168099,3168868,3168709,3168136,3168099,3168242,3168099,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168115,3168242,3168115,3168868,3168136,3168115,3168242,3168115,3168988,3168136,3168115,3168115,3168988,3168136,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168673,3168673</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L2 W15/25; N=116; EHP=7066.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x13,medium:83x6,swarm:84x32,heavy:88x11,medium:108x6,medium:123x5</t>
+          <t>L2 W15/25; N=116; EHP=11349.009383; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x13,heavy:88x11,medium:83x6,medium:108x6,medium:123x5,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3170136,3170673,3170242,3170019,3170668,3170709,3170136,3170673,3170242,3170019,3170668,3170709,3170136,3170673,3170242,3170019,3170668,3170709,3170136,3170673,3170242,3170091,3170668,3170709,3170136,3170673,3170242,3170091,3170668,3170709,3170136,3170673,3170242,3170091,3170668,3170709,3170136,3170673,3170242,3170099,3170868,3170709,3170136,3170673,3170242,3170099,3170868,3170709,3170136,3170673,3170242,3170099,3170868,3170709,3170136,3170673,3170242,3170107,3170868,3170709,3170136,3170673,3170242,3170107,3170868,3170709,3170136,3170673,3170242,3170107,3170868,3170709,3170136,3170673,3170242,3170115,3170988,3170136,3170673,3170242,3170115,3170988,3170144,3170673,3170115,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170673,3170673,3170673,3170673</t>
+          <t>3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170115,3170242,3170115,3170988,3170136,3170115,3170242,3170115,3170988,3170144,3170115,3170115,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170673,3170673,3170673,3170673</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L2 W16/25; N=122; EHP=7208.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x14,medium:83x6,swarm:84x34,heavy:88x12,medium:108x6,medium:123x6</t>
+          <t>L2 W16/25; N=122; EHP=11579.277913; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x14,heavy:88x12,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3172136,3172673,3172242,3172019,3172668,3172709,3172136,3172673,3172242,3172019,3172668,3172709,3172136,3172673,3172242,3172019,3172668,3172709,3172136,3172673,3172242,3172091,3172668,3172709,3172136,3172673,3172242,3172091,3172668,3172709,3172136,3172673,3172242,3172091,3172668,3172709,3172136,3172673,3172242,3172099,3172868,3172709,3172136,3172673,3172242,3172099,3172868,3172709,3172136,3172673,3172242,3172099,3172868,3172709,3172136,3172673,3172242,3172107,3172868,3172709,3172136,3172673,3172242,3172107,3172868,3172709,3172136,3172673,3172242,3172107,3172868,3172709,3172136,3172673,3172242,3172115,3172988,3172136,3172673,3172242,3172115,3172988,3172136,3172673,3172242,3172115,3172988,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172673,3172673</t>
+          <t>3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172115,3172242,3172115,3172988,3172136,3172115,3172242,3172115,3172988,3172136,3172115,3172242,3172115,3172988,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172673,3172673</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L2 W17/25; N=128; EHP=7353.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x15,medium:83x6,swarm:84x35,heavy:88x12,medium:108x6,medium:123x7</t>
+          <t>L2 W17/25; N=128; EHP=11805.770179; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x15,heavy:88x12,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3174136,3174673,3174242,3174019,3174668,3174709,3174136,3174673,3174242,3174019,3174668,3174709,3174136,3174673,3174242,3174019,3174668,3174709,3174136,3174673,3174242,3174091,3174668,3174709,3174136,3174673,3174242,3174091,3174668,3174709,3174136,3174673,3174242,3174091,3174668,3174709,3174136,3174673,3174242,3174099,3174668,3174709,3174136,3174673,3174242,3174099,3174868,3174709,3174136,3174673,3174242,3174099,3174868,3174709,3174136,3174673,3174242,3174099,3174868,3174709,3174136,3174673,3174242,3174107,3174868,3174709,3174136,3174673,3174242,3174107,3174868,3174709,3174136,3174673,3174242,3174107,3174868,3174709,3174136,3174673,3174242,3174115,3174868,3174136,3174673,3174242,3174115,3174988,3174136,3174673,3174242,3174115,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174673,3174673,3174673,3174673</t>
+          <t>3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174099,3174242,3174099,3174668,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174115,3174242,3174115,3174868,3174136,3174115,3174242,3174115,3174988,3174136,3174115,3174242,3174115,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174673,3174673,3174673,3174673</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L2 W18/25; N=134; EHP=7859.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x16,medium:83x7,swarm:84x37,heavy:88x13,medium:108x7,medium:123x6</t>
+          <t>L2 W18/25; N=134; EHP=12620.575360; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x16,heavy:88x13,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3176136,3176673,3176242,3176019,3176668,3176709,3176136,3176673,3176242,3176019,3176668,3176709,3176136,3176673,3176242,3176019,3176668,3176709,3176136,3176673,3176242,3176019,3176668,3176709,3176136,3176673,3176242,3176091,3176668,3176709,3176136,3176673,3176242,3176091,3176668,3176709,3176136,3176673,3176242,3176091,3176668,3176709,3176136,3176673,3176242,3176099,3176868,3176709,3176136,3176673,3176242,3176099,3176868,3176709,3176136,3176673,3176242,3176099,3176868,3176709,3176136,3176673,3176242,3176107,3176868,3176709,3176136,3176673,3176242,3176107,3176868,3176709,3176136,3176673,3176242,3176107,3176868,3176709,3176136,3176673,3176242,3176107,3176868,3176709,3176136,3176673,3176242,3176115,3176988,3176136,3176673,3176242,3176115,3176988,3176136,3176673,3176115,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176673,3176673,3176673,3176673,3176673</t>
+          <t>3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176115,3176242,3176115,3176988,3176136,3176115,3176242,3176115,3176988,3176136,3176115,3176115,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176673,3176673,3176673,3176673,3176673</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L2 W19/25; N=140; EHP=9101.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x16,fast:30x16,medium:83x7,swarm:84x39,heavy:88x14,medium:108x7,medium:123x7</t>
+          <t>L2 W19/25; N=140; EHP=14617.416655; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x16,heavy:88x14,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3178136,3178673,3178242,3178019,3178668,3178709,3178136,3178673,3178242,3178019,3178668,3178709,3178136,3178673,3178242,3178019,3178668,3178709,3178136,3178673,3178242,3178091,3178668,3178709,3178136,3178673,3178242,3178091,3178668,3178709,3178136,3178673,3178242,3178091,3178668,3178709,3178136,3178673,3178242,3178091,3178668,3178709,3178136,3178673,3178242,3178099,3178868,3178709,3178136,3178673,3178242,3178099,3178868,3178709,3178136,3178673,3178242,3178099,3178868,3178709,3178136,3178673,3178242,3178107,3178868,3178709,3178136,3178673,3178242,3178107,3178868,3178709,3178136,3178673,3178242,3178107,3178868,3178709,3178136,3178673,3178242,3178107,3178868,3178709,3178136,3178673,3178242,3178115,3178988,3178136,3178673,3178242,3178115,3178988,3178136,3178673,3178242,3178115,3178988,3178136,3178673,3178115,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178673,3178673,3178673</t>
+          <t>3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178115,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178673,3178673,3178673</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L2 W20/25; N=146; EHP=15289.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x17,medium:83x7,swarm:84x40,heavy:88x14,medium:108x7,medium:123x7</t>
+          <t>L2 W20/25; N=146; EHP=24562.981882; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x17,heavy:88x14,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>173</v>
+        <v>280</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>166</v>
+        <v>250</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1158,18 +1158,18 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016787,10016790,10016787,10016794,10016793,10016788,10016787,10016790,10016787,10016795,10016788,10016787,10016790,10016787,10016795,10016788,10016787,10016790,10016787,10016795,10016788,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016792,10016792,10016792,10016792</t>
+          <t>10016788,10048480,10016790,10048480,10016791,10016793,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10016790,10048480,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016785,10016791,10016793,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10048481,10016790,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10016788,10048481,10016790,10048481,10016794,10016793,10016788,10048481,10016790,10048481,10016794,10016793,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016790,10016786,10016794,10016793,10016788,10016786,10016790,10016786,10016794,10016793,10016788,10016788,10016787,10016790,10016787,10016794,10016793,10016788,10016787,10016790,10016787,10016795,10016788,10016788,10016787,10016790,10016787,10016795,10016788,10016787,10016787,10016790,10016787,10016795,10016788,10016788,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016789,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016789,10016792,10016792,10016792,10016792,10016792,10016792,10016788,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016793,10016788,10048480,10016790,10048480,10016791,10016793,10016788,10016785,10016790,10016790,10016785,10016791,10016793,10016788,10016785,10016790,10016785,10016791,10016793,10016788,10016788,10016790,10016790,10016788,10016791,10016793,10016788,10016792,10016792,10016790,10016789,10016791,10016793,10016788,10016792,10016792,10016790,10016789,10016794,10016793,10016788,10016789,10016790,10016790,10016789,10016794,10016793,10016788,10016789,10016790,10016789,10016789,10016794,10016793,10016788,10016789,10016790,10016789,10016789,10016794,10016793,10016788,10016789,10016790,10016789,10016794,10016794,10016793,10016788,10016789,10016790,10016792,10016794,10016793,10016793,10016788,10016792,10016790,10016790,10016794,10016793,10016793,10016788,10016790,10016790,10016793,10016794,10016793,10016788,10016788,10016793,10016790,10016790,10016795,10016788,10016788,10016788,10016790,10016791,10016795,10016788,10016790,10016790,10016793,10016793,10016795,10016788,10016792,10016795,10016789,10016792,10016795,10016795,10016789,10016792,10016795,10016789,10016792,10016795,10016795,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016789,10016789,10016792,10016789,10016792,10016792,10016792,10016792,10016792,10016792,10016792,10016788,10016792,10016790,10016789,10016791,10016791,10016793,10016788,10016792,10016790,10016789,10016791,10016793,10016793,10016788,10016789,10016790,10016789,10016791,10016793,10016788,10016788,10016789,10016790,10016789,10016791,10016793,10016788,10016788,10016789,10016790,10016789,10016791,10016793,10016788,10016789,10016789,10016790,10016789,10016791,10016793,10016788,10016789,10016790,10016790,10016792,10016791,10016793,10016788,10016792,10016790,10016790,10016790,10016794,10016793,10016788,10016790,10016790,10016793,10016793,10016794,10016793,10016788,10016793,10016790,10016790,10016794,10016794,10016793,10016788,10016790,10016790,10016793,10016794,10016794,10016793,10016788,10016793,10016790,10016790,10016794,10016793,10016793,10016788,10016790,10016790,10016793,10016794,10016793,10016788,10016788,10016793,10016790,10016790,10016794,10016793,10016788,10016788,10016790,10016790,10016793,10016794,10016793,10016788,10016793,10016793,10016790,10016790,10016795,10016788,10016788,10016790,10016794,10016794,10016795,10016788,10016790,10016790,10016793,10016795,10016795,10016788,10016792,10016795,10016789,10016792,10016795,10016789,10016789,10016792,10016795,10016789,10016792,10016795,10016789,10016792,10016792,10016789,10016792,10016789,10016792,10016789,10016792,10016792,10016789,10016792,10016789</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L2 W21/25; N=152; EHP=25041.438124; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x18,heavy:88x15,medium:83x7,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
+          <t>L2 W21/25; N=492; EHP=861902.536456; air:48; ground:444 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1179,18 +1179,18 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10048483,10016801,10048483,10016802,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016798,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016803,10016803,10016803,10016803</t>
+          <t>10016799,10048482,10016801,10048482,10016802,10016804,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016796,10016802,10016804,10016804,10016799,10016796,10016796,10016801,10016796,10016802,10016804,10016799,10048483,10016801,10048483,10016802,10016802,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10016799,10048483,10016801,10048483,10016805,10016804,10016799,10048483,10016801,10048483,10016805,10016804,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016805,10016804,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016799,10016797,10016801,10016797,10016805,10016804,10016799,10016798,10016801,10016798,10016806,10016799,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016801,10016798,10016806,10016799,10016798,10016798,10016798,10016806,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016800,10016803,10016800,10016803,10016803,10016803,10016803,10016803,10016803,10016803,10016799,10048482,10016801,10048482,10016802,10016804,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016802,10016804,10016799,10048482,10016801,10048482,10016802,10016804,10016799,10016799,10016796,10016801,10016796,10016802,10016804,10016799,10016796,10016801,10016800,10016802,10016802,10016804,10016799,10016803,10016801,10016800,10016802,10016804,10016804,10016799,10016803,10016801,10016800,10016802,10016804,10016804,10016799,10016800,10016801,10016800,10016805,10016804,10016799,10016799,10016800,10016801,10016800,10016805,10016804,10016799,10016800,10016800,10016801,10016800,10016805,10016804,10016799,10016800,10016800,10016801,10016800,10016805,10016804,10016799,10016800,10016801,10016801,10016800,10016805,10016804,10016799,10016803,10016801,10016803,10016803,10016805,10016804,10016799,10016804,10016801,10016801,10016801,10016805,10016804,10016799,10016801,10016801,10016804,10016806,10016806,10016799,10016802,10016801,10016799,10016806,10016799,10016804,10016804,10016801,10016801,10016806,10016799,10016799,10016801,10016801,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016806,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016803,10016803,10016803,10016803,10016803,10016803,10016799,10016800,10016801,10016806,10016806,10016802,10016804,10016799,10016800,10016801,10016800,10016800,10016802,10016804,10016799,10016800,10016801,10016800,10016802,10016802,10016804,10016799,10016800,10016801,10016800,10016802,10016804,10016804,10016799,10016800,10016801,10016800,10016802,10016804,10016804,10016799,10016800,10016801,10016800,10016802,10016804,10016799,10016799,10016800,10016801,10016803,10016802,10016804,10016799,10016803,10016803,10016801,10016801,10016802,10016804,10016799,10016801,10016801,10016801,10016804,10016805,10016804,10016799,10016804,10016801,10016801,10016801,10016805,10016804,10016799,10016801,10016801,10016804,10016804,10016805,10016804,10016799,10016804,10016801,10016801,10016801,10016805,10016804,10016799,10016801,10016801,10016804,10016805,10016805,10016804,10016799,10016804,10016801,10016801,10016805,10016804,10016804,10016799,10016801,10016801,10016804,10016805,10016804,10016804,10016799,10016804,10016801,10016801,10016806,10016799,10016799,10016799,10016801,10016805,10016806,10016799,10016801,10016801,10016804,10016804,10016806,10016799,10016806,10016799,10016806,10016800,10016800,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016803,10016806,10016800,10016803,10016806,10016800,10016803,10016800,10016800,10016803,10016800,10016803,10016800,10016803,10016800,10016800,10016803,10016800,10016803</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>240</v>
+        <v>433</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L2 W22/25; N=158; EHP=25548.287686; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x18,heavy:88x15,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
+          <t>L2 W22/25; N=511; EHP=889159.364401; air:51; ground:460 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1200,18 +1200,18 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016809,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016814,10016814,10016814,10016814</t>
+          <t>10016810,10048484,10016812,10048484,10016813,10016815,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10016810,10016807,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016813,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016815,10016810,10048485,10016812,10048485,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016816,10016815,10016810,10016808,10016808,10016812,10016808,10016816,10016815,10016810,10016810,10016808,10016812,10016808,10016816,10016815,10016810,10016808,10016812,10016808,10016816,10016815,10016815,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016812,10016809,10016817,10016810,10016810,10016809,10016812,10016809,10016817,10016810,10016809,10016809,10016817,10016811,10016814,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016817,10016811,10016814,10016817,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016814,10016814,10016814,10016814,10016814,10016814,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10048484,10016812,10048484,10048484,10016813,10016813,10016815,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10016810,10048484,10016812,10048484,10016813,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016815,10016810,10016807,10016812,10016807,10016813,10016815,10016810,10016817,10016812,10016812,10016814,10016813,10016815,10016810,10016817,10016812,10016812,10016814,10016813,10016815,10016810,10016811,10016812,10016811,10016811,10016816,10016815,10016810,10016811,10016812,10016811,10016816,10016816,10016815,10016810,10016811,10016812,10016811,10016816,10016816,10016815,10016810,10016811,10016812,10016811,10016816,10016815,10016815,10016810,10016811,10016812,10016811,10016816,10016815,10016810,10016810,10016814,10016812,10016814,10016816,10016815,10016810,10016810,10016812,10016812,10016815,10016816,10016815,10016810,10016815,10016815,10016812,10016812,10016816,10016815,10016810,10016812,10016812,10016812,10016815,10016817,10016810,10016813,10016812,10016810,10016817,10016817,10016810,10016815,10016812,10016812,10016817,10016810,10016810,10016810,10016812,10016817,10016811,10016814,10016817,10016811,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016814,10016814,10016817,10016811,10016814,10016811,10016814,10016811,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016814,10016814,10016814,10016814,10016814,10016810,10016811,10016811,10016812,10016817,10016813,10016815,10016810,10016811,10016811,10016812,10016811,10016813,10016815,10016810,10016811,10016812,10016812,10016811,10016813,10016815,10016810,10016811,10016812,10016811,10016811,10016813,10016815,10016810,10016811,10016812,10016811,10016811,10016813,10016815,10016810,10016811,10016812,10016811,10016813,10016813,10016815,10016810,10016811,10016812,10016814,10016813,10016815,10016815,10016810,10016814,10016812,10016812,10016813,10016815,10016815,10016810,10016812,10016812,10016815,10016816,10016815,10016810,10016810,10016815,10016812,10016812,10016816,10016815,10016810,10016812,10016812,10016812,10016815,10016816,10016815,10016810,10016815,10016815,10016812,10016812,10016816,10016815,10016810,10016812,10016812,10016812,10016815,10016816,10016815,10016810,10016815,10016812,10016812,10016812,10016816,10016815,10016810,10016812,10016812,10016815,10016815,10016816,10016815,10016810,10016815,10016812,10016812,10016816,10016816,10016815,10016810,10016812,10016812,10016815,10016817,10016810,10016810,10016816,10016812,10016810,10016817,10016810,10016815,10016815,10016812,10016812,10016817,10016810,10016812,10016817,10016817,10016817,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016811,10016814,10016817,10016811,10016814,10016817,10016811,10016811,10016814,10016811,10016814,10016811,10016814,10016811,10016814,10016814,10016811,10016814,10016811</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>220</v>
+        <v>433</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L2 W23/25; N=164; EHP=26063.722104; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x19,heavy:88x16,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
+          <t>L2 W23/25; N=531; EHP=911206.802258; air:55; ground:476 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1221,18 +1221,18 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016820,10016823,10016820,10016827,10016826,10016821,10016820,10016823,10016820,10016828,10016821,10016820,10016823,10016820,10016828,10016821,10016820,10016823,10016820,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016825,10016825,10016825,10016825,10016825</t>
+          <t>10016821,10048486,10016823,10048486,10016824,10016826,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10016821,10016818,10016823,10016818,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016824,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016826,10016821,10048487,10016823,10048487,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016827,10016826,10016821,10016819,10016823,10016819,10016819,10016827,10016826,10016821,10016821,10016819,10016823,10016819,10016827,10016826,10016821,10016819,10016823,10016819,10016827,10016826,10016826,10016821,10016820,10016823,10016820,10016827,10016826,10016821,10016820,10016823,10016820,10016828,10016828,10016821,10016820,10016823,10016820,10016828,10016821,10016820,10016823,10016820,10016828,10016822,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016825,10016828,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016825,10016825,10016825,10016825,10016825,10016825,10016821,10016821,10048486,10016823,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016826,10016826,10016821,10048486,10016823,10048486,10048486,10016824,10016826,10016821,10048486,10016823,10048486,10016824,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016821,10016818,10016823,10016818,10016824,10016826,10016821,10016818,10016823,10016818,10016824,10016826,10016826,10016821,10016818,10016823,10016828,10016824,10016826,10016821,10016822,10016822,10016823,10016828,10016827,10016826,10016821,10016825,10016825,10016823,10016825,10016827,10016826,10016821,10016825,10016823,10016823,10016825,10016827,10016826,10016821,10016825,10016823,10016825,10016825,10016827,10016826,10016821,10016825,10016823,10016825,10016827,10016827,10016826,10016821,10016825,10016823,10016825,10016827,10016827,10016826,10016821,10016825,10016823,10016825,10016827,10016826,10016826,10016821,10016823,10016823,10016826,10016827,10016826,10016821,10016821,10016826,10016823,10016823,10016827,10016826,10016821,10016821,10016823,10016823,10016826,10016828,10016821,10016824,10016823,10016823,10016821,10016828,10016821,10016826,10016823,10016823,10016828,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016828,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016822,10016825,10016828,10016822,10016825,10016822,10016825,10016822,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016825,10016825,10016825,10016825,10016825,10016825,10016825,10016825,10016821,10016825,10016823,10016822,10016824,10016826,10016821,10016821,10016825,10016823,10016822,10016824,10016826,10016821,10016825,10016825,10016823,10016825,10016824,10016826,10016821,10016825,10016825,10016823,10016825,10016824,10016826,10016821,10016825,10016823,10016823,10016825,10016824,10016826,10016821,10016825,10016823,10016825,10016825,10016824,10016826,10016821,10016825,10016823,10016825,10016824,10016824,10016826,10016821,10016825,10016823,10016825,10016824,10016824,10016826,10016821,10016825,10016823,10016823,10016827,10016826,10016826,10016821,10016823,10016823,10016826,10016827,10016826,10016821,10016821,10016826,10016823,10016823,10016827,10016826,10016821,10016821,10016823,10016823,10016826,10016827,10016826,10016821,10016826,10016826,10016823,10016823,10016827,10016826,10016821,10016823,10016823,10016823,10016826,10016827,10016826,10016821,10016826,10016823,10016823,10016823,10016827,10016826,10016821,10016823,10016823,10016826,10016826,10016827,10016826,10016821,10016826,10016823,10016823,10016827,10016827,10016826,10016821,10016823,10016823,10016826,10016828,10016821,10016821,10016827,10016823,10016821,10016828,10016821,10016826,10016826,10016823,10016823,10016828,10016822,10016825,10016828,10016822,10016822,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016825,10016828,10016822,10016825,10016828,10016822,10016825,10016825,10016822,10016825,10016822,10016825,10016822,10016825,10016822,10016822,10016825,10016822,10016825</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>300</v>
+        <v>433</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L2 W24/25; N=170; EHP=27896.490207; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x20,heavy:88x17,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
+          <t>L2 W24/25; N=551; EHP=975890.679999; air:58; ground:493 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1242,18 +1242,18 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10016832,10048488,10016834,10048488,10016835,10016837,10016839,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10048489,10016834,10048489,10016835,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836</t>
+          <t>10016832,10048488,10016834,10048488,10016835,10016837,10016837,10016839,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10016832,10048488,10016834,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016837,10016837,10016832,10016829,10016834,10016829,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10048489,10016834,10048489,10016835,10016837,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016838,10016837,10016832,10048489,10016834,10048489,10016838,10016837,10016832,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016837,10016832,10016830,10016830,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016834,10016830,10016838,10016837,10016832,10016830,10016834,10016830,10016838,10016837,10016832,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016832,10016831,10016834,10016834,10016831,10016840,10016832,10016831,10016834,10016831,10016840,10016833,10016836,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016833,10016836,10016833,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016832,10048488,10016834,10016834,10048488,10016835,10016837,10016839,10016832,10048488,10016834,10048488,10016835,10016837,10016837,10016832,10048488,10016834,10048488,10048488,10016835,10016837,10016832,10048488,10016834,10048488,10016835,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016832,10016829,10016834,10016829,10016835,10016837,10016832,10016829,10016834,10016829,10016835,10016837,10016837,10016832,10016829,10016834,10016836,10016835,10016837,10016832,10016832,10016840,10016834,10016836,10016835,10016837,10016832,10016833,10016833,10016834,10016833,10016838,10016837,10016832,10016833,10016834,10016834,10016833,10016838,10016837,10016832,10016833,10016834,10016834,10016833,10016838,10016837,10016832,10016833,10016834,10016833,10016833,10016838,10016837,10016832,10016833,10016834,10016833,10016838,10016838,10016837,10016832,10016836,10016834,10016836,10016838,10016838,10016837,10016832,10016832,10016834,10016835,10016838,10016837,10016837,10016832,10016834,10016834,10016837,10016838,10016837,10016832,10016832,10016837,10016834,10016834,10016840,10016832,10016832,10016832,10016834,10016835,10016840,10016832,10016834,10016834,10016837,10016837,10016840,10016832,10016835,10016834,10016832,10016840,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016836,10016840,10016833,10016836,10016833,10016836,10016833,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016833,10016836,10016833,10016836,10016833,10016836,10016833,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016836,10016832,10016836,10016834,10016833,10016835,10016837,10016839,10016839,10016832,10016840,10016834,10016836,10016835,10016837,10016832,10016832,10016833,10016834,10016833,10016835,10016837,10016832,10016832,10016833,10016834,10016833,10016835,10016837,10016832,10016833,10016833,10016834,10016833,10016835,10016837,10016832,10016833,10016834,10016834,10016833,10016835,10016837,10016832,10016833,10016834,10016834,10016833,10016835,10016837,10016832,10016836,10016834,10016836,10016836,10016835,10016837,10016832,10016832,10016834,10016835,10016835,10016835,10016837,10016832,10016834,10016834,10016837,10016838,10016838,10016837,10016832,10016837,10016834,10016834,10016838,10016837,10016837,10016832,10016834,10016834,10016837,10016838,10016837,10016837,10016832,10016837,10016834,10016834,10016838,10016837,10016832,10016832,10016834,10016834,10016837,10016838,10016837,10016832,10016837,10016837,10016834,10016834,10016838,10016837,10016832,10016834,10016834,10016834,10016837,10016838,10016837,10016832,10016837,10016834,10016834,10016834,10016838,10016837,10016832,10016834,10016834,10016834,10016837,10016840,10016832,10016838,10016834,10016832,10016840,10016840,10016832,10016837,10016834,10016834,10016840,10016832,10016832,10016832,10016834,10016840,10016840,10016833,10016836,10016840,10016840,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016833,10016836,10016840,10016833,10016836,10016840,10016833,10016836,10016836,10016833,10016836,10016833,10016836,10016833,10016836,10016836,10016833,10016836,10016833</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>155</v>
+        <v>435</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L2 W25/25; N=176; EHP=55692.679138; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x21,heavy:88x17,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x28 | manual: L1-scaled</t>
+          <t>L2 W25/25; N=571; EHP=1271000.975038; air:60; ground:511 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1263,18 +1263,18 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144,3140144</t>
+          <t>3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140136,3140144,3140144,3140144,3140144,3140144</t>
         </is>
       </c>
       <c r="D9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>300</v>
+        <v>475</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L2 W1/25; N=32; EHP=281.663449; normal:17x16,normal:18x16 | manual: L1-scaled</t>
+          <t>L2 W1/25; N=21; EHP=409.600023; air:0; ground:21 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101</t>
         </is>
       </c>
     </row>
@@ -1284,18 +1284,18 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144,3142144</t>
+          <t>3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142136,3142144,3142144,3142144,3142144,3142144,3142144,3142144</t>
         </is>
       </c>
       <c r="D10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>290</v>
+        <v>447</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L2 W2/25; N=38; EHP=350.229135; normal:17x19,normal:18x19 | manual: L1-scaled</t>
+          <t>L2 W2/25; N=26; EHP=512.000008; air:0; ground:26 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101</t>
         </is>
       </c>
     </row>
@@ -1305,18 +1305,18 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144136,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144144,3144136,3144136,3144136,3144136,3144136</t>
+          <t>3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144136,3144144,3144144,3144144,3144144</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>260</v>
+        <v>438</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L2 W3/25; N=44; EHP=481.932928; normal:17x19,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
+          <t>L2 W3/25; N=30; EHP=707.200014; air:0; ground:30 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101</t>
         </is>
       </c>
     </row>
@@ -1326,18 +1326,18 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146144,3146136,3146136,3146136,3146136,3146136,3146136</t>
+          <t>3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146144,3146144,3146144,3146144,3146144</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L2 W4/25; N=50; EHP=633.394156; normal:17x21,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
+          <t>L2 W4/25; N=34; EHP=931.200012; air:0; ground:34 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101</t>
         </is>
       </c>
     </row>
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3148136,3148019,3148019,3148668,3148136,3148091,3148091,3148668,3148136,3148091,3148091,3148668,3148136,3148099,3148099,3148668,3148136,3148107,3148107,3148988,3148136,3148107,3148107,3148988,3148136,3148115,3148115,3148988,3148136,3148673,3148988,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148673,3148144,3148673,3148144,3148673,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144</t>
+          <t>3148136,3148019,3148019,3148668,3148136,3148091,3148091,3148668,3148668,3148136,3148091,3148091,3148668,3148136,3148988,3148136,3148668,3148668,3148136,3148136,3148673,3148988,3148136,3148136,3148673,3148673,3148988,3148136,3148136,3148673,3148988,3148136,3148673,3148673,3148988,3148136,3148673,3148136,3148673,3148136,3148136,3148673,3148136,3148673,3148136,3148673,3148144,3148673,3148673,3148144,3148673,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148136,3148673,3148988,3148668,3148136,3148136,3148673,3148673,3148668,3148136,3148136,3148673,3148668,3148136,3148144,3148144,3148673,3148668,3148136,3148144,3148144,3148988,3148988,3148136,3148144,3148144,3148988,3148136,3148144,3148144,3148144,3148988,3148136,3148673,3148988,3148136,3148673,3148136,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148136,3148673,3148144,3148673,3148144,3148673,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148144,3148136,3148144,3148673,3148668,3148668,3148136,3148144,3148144,3148668,3148136,3148144,3148144,3148144,3148668,3148136,3148144,3148136,3148668,3148136,3148668,3148668,3148136,3148988,3148136,3148668,3148136,3148988,3148988,3148136,3148988,3148136,3148988,3148136,3148673,3148988,3148988,3148136,3148673,3148136,3148673,3148136,3148673,3148136,3148136,3148673,3148136,3148673,3148144,3148673,3148144,3148144,3148673,3148144,3148144</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>250</v>
+        <v>460</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L2 W5/25; N=56; EHP=1147.540637; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x4,medium:123x4,normal:17x13,normal:18x13,swarm:84x8 | manual: L1-scaled</t>
+          <t>L2 W5/25; N=182; EHP=52021.606716; air:6; ground:176 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1368,18 +1368,18 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3150136,3150019,3150019,3150668,3150136,3150091,3150091,3150668,3150136,3150091,3150091,3150668,3150136,3150099,3150099,3150668,3150136,3150107,3150107,3150668,3150136,3150115,3150115,3150988,3150136,3150115,3150115,3150988,3150136,3150673,3150988,3150136,3150673,3150988,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150144,3150673,3150144,3150673,3150144,3150673,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144</t>
+          <t>3150136,3150019,3150019,3150668,3150136,3150091,3150091,3150668,3150668,3150136,3150091,3150091,3150668,3150136,3150099,3150099,3150668,3150136,3150136,3150673,3150673,3150668,3150136,3150673,3150136,3150988,3150136,3150136,3150673,3150136,3150988,3150136,3150673,3150988,3150136,3150136,3150673,3150988,3150136,3150673,3150136,3150673,3150136,3150136,3150673,3150136,3150673,3150136,3150673,3150144,3150673,3150673,3150144,3150673,3150144,3150673,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150136,3150673,3150988,3150668,3150668,3150136,3150988,3150136,3150668,3150136,3150673,3150136,3150136,3150668,3150136,3150673,3150136,3150668,3150136,3150136,3150673,3150144,3150668,3150136,3150673,3150144,3150988,3150988,3150136,3150144,3150144,3150988,3150136,3150673,3150988,3150988,3150136,3150673,3150988,3150136,3150673,3150136,3150673,3150673,3150136,3150673,3150136,3150673,3150136,3150673,3150144,3150144,3150673,3150144,3150673,3150144,3150673,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150144,3150136,3150673,3150144,3150144,3150668,3150136,3150673,3150144,3150668,3150136,3150144,3150144,3150144,3150668,3150136,3150144,3150144,3150668,3150668,3150136,3150144,3150144,3150668,3150136,3150668,3150136,3150136,3150988,3150136,3150668,3150136,3150988,3150136,3150673,3150673,3150988,3150136,3150673,3150988,3150136,3150673,3150136,3150136,3150673,3150136,3150673,3150136,3150673,3150136,3150136,3150673,3150144,3150673,3150144,3150673,3150144,3150673,3150673,3150144,3150144,3150144</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>310</v>
+        <v>447</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L2 W6/25; N=62; EHP=1169.646199; air:2x2,air:11x4,air:12x2,air:13x2,air:14x4,medium:83x5,medium:123x4,normal:17x14,normal:18x15,swarm:84x10 | manual: L1-scaled</t>
+          <t>L2 W6/25; N=202; EHP=58215.651053; air:8; ground:194 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1389,18 +1389,18 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3152136,3152019,3152019,3152668,3152136,3152019,3152019,3152668,3152136,3152091,3152091,3152668,3152136,3152099,3152099,3152668,3152136,3152099,3152099,3152668,3152136,3152107,3152107,3152988,3152136,3152115,3152115,3152988,3152136,3152115,3152115,3152988,3152136,3152673,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152673,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144</t>
+          <t>3152136,3152019,3152019,3152668,3152136,3152019,3152019,3152668,3152668,3152136,3152091,3152091,3152668,3152136,3152099,3152099,3152668,3152136,3152099,3152099,3152668,3152136,3152136,3152107,3152136,3152988,3152136,3152673,3152136,3152988,3152988,3152136,3152673,3152136,3152988,3152136,3152673,3152988,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152673,3152673,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152136,3152136,3152673,3152988,3152668,3152136,3152988,3152136,3152668,3152668,3152136,3152673,3152136,3152668,3152136,3152673,3152136,3152136,3152668,3152136,3152673,3152144,3152668,3152136,3152136,3152673,3152144,3152988,3152136,3152144,3152144,3152988,3152988,3152136,3152144,3152144,3152988,3152136,3152673,3152988,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152136,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152144,3152673,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152144,3152136,3152136,3152673,3152144,3152668,3152136,3152673,3152144,3152668,3152668,3152136,3152144,3152144,3152668,3152136,3152144,3152144,3152144,3152668,3152136,3152144,3152144,3152668,3152136,3152136,3152668,3152136,3152988,3152136,3152668,3152136,3152988,3152988,3152136,3152668,3152136,3152988,3152136,3152673,3152988,3152988,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152673,3152136,3152673,3152136,3152673,3152136,3152673,3152673,3152136,3152673,3152144,3152673,3152144,3152673,3152144,3152144,3152673,3152144,3152144</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L2 W7/25; N=68; EHP=1360.883823; air:2x4,air:11x2,air:12x4,air:13x2,air:14x4,medium:83x5,medium:123x5,normal:17x16,normal:18x15,swarm:84x11 | manual: L1-scaled</t>
+          <t>L2 W7/25; N=221; EHP=68032.667284; air:11; ground:210 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1410,18 +1410,18 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3154136,3154019,3154019,3154668,3154136,3154019,3154019,3154668,3154136,3154091,3154091,3154668,3154136,3154091,3154091,3154668,3154136,3154099,3154099,3154668,3154136,3154099,3154099,3154668,3154136,3154107,3154107,3154988,3154136,3154107,3154107,3154988,3154136,3154115,3154115,3154988,3154136,3154673,3154988,3154136,3154673,3154988,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154144,3154673,3154144,3154673,3154144,3154673,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144</t>
+          <t>3154136,3154019,3154019,3154668,3154136,3154019,3154019,3154668,3154668,3154136,3154091,3154091,3154668,3154136,3154091,3154091,3154668,3154136,3154099,3154099,3154668,3154668,3154136,3154099,3154099,3154668,3154136,3154107,3154107,3154988,3154136,3154673,3154136,3154136,3154988,3154136,3154673,3154136,3154988,3154136,3154136,3154673,3154988,3154136,3154673,3154988,3154136,3154673,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154136,3154673,3154136,3154673,3154144,3154673,3154144,3154144,3154673,3154144,3154673,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154136,3154673,3154988,3154988,3154668,3154136,3154988,3154136,3154668,3154136,3154136,3154673,3154136,3154668,3154136,3154673,3154136,3154668,3154668,3154136,3154673,3154144,3154668,3154136,3154673,3154144,3154144,3154668,3154136,3154144,3154144,3154988,3154136,3154136,3154144,3154144,3154988,3154136,3154144,3154144,3154988,3154988,3154136,3154673,3154988,3154136,3154673,3154988,3154988,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154136,3154673,3154136,3154673,3154136,3154673,3154144,3154144,3154673,3154144,3154673,3154144,3154673,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154144,3154136,3154136,3154673,3154144,3154668,3154136,3154673,3154144,3154668,3154668,3154136,3154144,3154144,3154668,3154136,3154144,3154144,3154144,3154668,3154136,3154144,3154144,3154668,3154136,3154136,3154668,3154136,3154668,3154136,3154668,3154136,3154136,3154988,3154136,3154668,3154136,3154988,3154136,3154988,3154988,3154136,3154988,3154136,3154673,3154988,3154136,3154673,3154673,3154988,3154136,3154673,3154136,3154673,3154136,3154136,3154673,3154136,3154673,3154136,3154673,3154136,3154673,3154673,3154144,3154673,3154144,3154673,3154144,3154673,3154673,3154144,3154144,3154144</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L2 W8/25; N=74; EHP=1766.747741; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,medium:83x6,medium:123x5,normal:17x17,normal:18x17,swarm:84x11 | manual: L1-scaled</t>
+          <t>L2 W8/25; N=241; EHP=88631.515085; air:14; ground:227 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1431,18 +1431,18 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3156136,3156019,3156019,3156668,3156136,3156019,3156019,3156668,3156136,3156091,3156091,3156668,3156136,3156091,3156091,3156668,3156136,3156099,3156099,3156668,3156136,3156099,3156099,3156668,3156136,3156107,3156107,3156988,3156136,3156107,3156107,3156988,3156136,3156115,3156115,3156988,3156136,3156115,3156115,3156988,3156136,3156673,3156988,3156136,3156673,3156988,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144</t>
+          <t>3156136,3156019,3156019,3156668,3156136,3156019,3156019,3156668,3156668,3156136,3156091,3156091,3156668,3156136,3156091,3156091,3156668,3156136,3156099,3156099,3156668,3156668,3156136,3156099,3156099,3156668,3156136,3156107,3156107,3156988,3156136,3156107,3156107,3156988,3156136,3156136,3156115,3156136,3156988,3156136,3156673,3156144,3156988,3156136,3156136,3156673,3156988,3156136,3156673,3156988,3156136,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156673,3156136,3156673,3156136,3156673,3156144,3156673,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156136,3156673,3156988,3156668,3156136,3156988,3156136,3156136,3156668,3156136,3156673,3156136,3156668,3156136,3156136,3156673,3156136,3156668,3156136,3156673,3156144,3156668,3156668,3156136,3156673,3156144,3156668,3156136,3156673,3156144,3156144,3156988,3156136,3156144,3156144,3156988,3156136,3156136,3156144,3156144,3156988,3156136,3156144,3156144,3156988,3156988,3156136,3156673,3156988,3156136,3156673,3156988,3156988,3156136,3156673,3156136,3156673,3156136,3156673,3156136,3156136,3156673,3156136,3156673,3156136,3156673,3156144,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156673,3156673,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156144,3156136,3156673,3156144,3156668,3156136,3156673,3156673,3156144,3156668,3156136,3156144,3156144,3156668,3156668,3156136,3156144,3156144,3156668,3156136,3156144,3156144,3156144,3156668,3156136,3156668,3156136,3156668,3156136,3156668,3156668,3156136,3156988,3156136,3156668,3156136,3156988,3156988,3156136,3156988,3156136,3156988,3156136,3156988,3156136,3156136,3156988,3156136,3156673,3156988,3156136,3156673,3156673,3156988,3156136,3156673,3156136,3156673,3156136,3156673,3156673,3156136,3156673,3156136,3156673,3156136,3156673,3156144,3156144,3156673,3156144,3156673,3156144,3156673,3156144,3156144,3156673,3156144,3156144</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>260</v>
+        <v>418</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L2 W9/25; N=80; EHP=2265.005618; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x6,medium:123x6,normal:17x18,normal:18x18,swarm:84x12 | manual: L1-scaled</t>
+          <t>L2 W9/25; N=260; EHP=112784.281412; air:17; ground:243 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1452,18 +1452,18 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3158136,3158019,3158019,3158668,3158136,3158019,3158019,3158668,3158136,3158091,3158091,3158668,3158136,3158091,3158091,3158668,3158136,3158099,3158099,3158668,3158136,3158099,3158099,3158668,3158136,3158107,3158107,3158988,3158136,3158107,3158107,3158988,3158136,3158115,3158115,3158988,3158136,3158115,3158115,3158988,3158136,3158673,3158988,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144</t>
+          <t>3158136,3158019,3158019,3158668,3158136,3158019,3158019,3158668,3158668,3158136,3158091,3158091,3158668,3158136,3158091,3158091,3158668,3158136,3158099,3158099,3158668,3158136,3158136,3158099,3158099,3158668,3158136,3158107,3158107,3158988,3158136,3158107,3158107,3158988,3158136,3158136,3158115,3158115,3158988,3158136,3158115,3158136,3158988,3158136,3158673,3158988,3158988,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158673,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158136,3158673,3158988,3158668,3158668,3158136,3158988,3158136,3158668,3158136,3158673,3158673,3158136,3158668,3158136,3158673,3158136,3158668,3158136,3158136,3158673,3158136,3158668,3158136,3158673,3158144,3158668,3158668,3158136,3158673,3158144,3158988,3158136,3158673,3158673,3158144,3158988,3158136,3158144,3158144,3158988,3158136,3158136,3158144,3158144,3158988,3158136,3158673,3158988,3158136,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158673,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158673,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158144,3158136,3158673,3158144,3158668,3158668,3158136,3158673,3158144,3158668,3158136,3158673,3158144,3158144,3158668,3158136,3158144,3158144,3158668,3158136,3158144,3158144,3158144,3158668,3158136,3158144,3158144,3158668,3158668,3158136,3158144,3158136,3158988,3158136,3158668,3158136,3158136,3158988,3158136,3158668,3158136,3158988,3158136,3158668,3158668,3158136,3158988,3158136,3158673,3158988,3158136,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158136,3158136,3158673,3158136,3158673,3158136,3158673,3158136,3158673,3158673,3158136,3158673,3158136,3158673,3158144,3158673,3158673,3158144,3158673,3158144,3158673,3158144,3158673,3158144,3158144,3158144,3158144,3158144</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>215</v>
+        <v>417</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L2 W10/25; N=86; EHP=4180.799826; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x6,medium:123x6,normal:17x20,normal:18x20,swarm:84x14 | manual: L1-scaled</t>
+          <t>L2 W10/25; N=280; EHP=160595.065133; air:19; ground:261 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1473,18 +1473,18 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3160136,3160019,3160242,3160019,3160668,3160709,3160136,3160019,3160242,3160019,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160099,3160242,3160099,3160668,3160709,3160136,3160099,3160242,3160099,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160709,3160136,3160115,3160242,3160115,3160988,3160136,3160115,3160242,3160115,3160988,3160136,3160673,3160988,3160144,3160673,3160988,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160673</t>
+          <t>3160136,3160019,3160242,3160019,3160668,3160709,3160709,3160136,3160019,3160242,3160019,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160668,3160709,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160136,3160091,3160242,3160091,3160668,3160709,3160136,3160099,3160242,3160099,3160668,3160709,3160709,3160136,3160099,3160242,3160099,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160988,3160709,3160136,3160107,3160242,3160107,3160988,3160709,3160136,3160136,3160115,3160242,3160115,3160988,3160136,3160115,3160242,3160115,3160988,3160136,3160673,3160673,3160988,3160144,3160673,3160988,3160144,3160673,3160144,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160144,3160673,3160144,3160673,3160673,3160673,3160136,3160136,3160709,3160242,3160242,3160668,3160709,3160136,3160136,3160242,3160242,3160709,3160668,3160709,3160136,3160709,3160709,3160242,3160242,3160668,3160709,3160136,3160988,3160242,3160242,3160673,3160668,3160709,3160136,3160988,3160242,3160673,3160673,3160668,3160709,3160136,3160673,3160242,3160673,3160673,3160668,3160709,3160136,3160673,3160242,3160673,3160988,3160988,3160709,3160136,3160673,3160242,3160673,3160988,3160709,3160709,3160136,3160242,3160242,3160709,3160988,3160709,3160709,3160136,3160709,3160242,3160242,3160988,3160136,3160136,3160136,3160242,3160668,3160988,3160136,3160673,3160988,3160144,3160144,3160673,3160988,3160144,3160673,3160144,3160673,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160144,3160673,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160144,3160673,3160673,3160673,3160136,3160144,3160242,3160242,3160988,3160668,3160709,3160136,3160673,3160242,3160242,3160673,3160668,3160709,3160136,3160673,3160242,3160673,3160673,3160668,3160709,3160136,3160673,3160242,3160673,3160668,3160668,3160709,3160136,3160673,3160242,3160242,3160668,3160668,3160709,3160136,3160242,3160242,3160709,3160668,3160709,3160709,3160136,3160709,3160242,3160242,3160988,3160709,3160136,3160136,3160242,3160242,3160709,3160988,3160709,3160136,3160136,3160709,3160242,3160242,3160988,3160709,3160136,3160242,3160242,3160242,3160709,3160988,3160136,3160988,3160242,3160136,3160136,3160988,3160136,3160673,3160988,3160144,3160673,3160673,3160988,3160144,3160673,3160144,3160673,3160144,3160673,3160673,3160144,3160673,3160144</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>260</v>
+        <v>399</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L2 W11/25; N=92; EHP=4262.207193; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x11,heavy:88x9,medium:83x6,medium:123x7,normal:17x12,normal:18x11,swarm:84x14 | manual: L1-scaled</t>
+          <t>L2 W11/25; N=299; EHP=175152.025124; air:22; ground:277 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1494,18 +1494,18 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3162136,3162019,3162242,3162019,3162668,3162709,3162136,3162019,3162242,3162019,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162107,3162242,3162107,3162988,3162709,3162136,3162107,3162242,3162107,3162988,3162709,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162115,3162988,3162144,3162673,3162988,3162144,3162673,3162988,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162673</t>
+          <t>3162136,3162019,3162242,3162019,3162668,3162709,3162709,3162136,3162019,3162242,3162019,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162668,3162709,3162136,3162091,3162242,3162091,3162668,3162709,3162136,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162709,3162136,3162099,3162242,3162099,3162668,3162709,3162136,3162107,3162242,3162107,3162988,3162988,3162709,3162136,3162107,3162242,3162107,3162988,3162709,3162136,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162242,3162115,3162988,3162136,3162115,3162115,3162988,3162988,3162144,3162673,3162988,3162144,3162673,3162988,3162144,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162144,3162673,3162673,3162673,3162136,3162019,3162242,3162709,3162668,3162668,3162709,3162136,3162709,3162242,3162242,3162668,3162668,3162709,3162136,3162242,3162242,3162136,3162668,3162709,3162709,3162136,3162988,3162242,3162673,3162668,3162709,3162136,3162136,3162988,3162242,3162673,3162668,3162709,3162136,3162673,3162673,3162242,3162673,3162668,3162709,3162136,3162673,3162673,3162242,3162673,3162668,3162709,3162136,3162673,3162242,3162242,3162673,3162988,3162709,3162136,3162673,3162242,3162242,3162242,3162988,3162709,3162136,3162242,3162242,3162709,3162709,3162988,3162136,3162668,3162242,3162136,3162988,3162136,3162136,3162709,3162136,3162988,3162144,3162673,3162988,3162144,3162144,3162673,3162988,3162144,3162673,3162144,3162673,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162673,3162673,3162144,3162673,3162144,3162673,3162673,3162673,3162136,3162136,3162988,3162242,3162673,3162668,3162709,3162136,3162136,3162673,3162242,3162673,3162668,3162709,3162136,3162673,3162673,3162242,3162673,3162668,3162709,3162136,3162673,3162242,3162242,3162673,3162668,3162709,3162136,3162673,3162242,3162242,3162242,3162668,3162709,3162136,3162242,3162242,3162709,3162709,3162668,3162709,3162136,3162709,3162242,3162242,3162668,3162668,3162709,3162136,3162242,3162242,3162709,3162988,3162709,3162709,3162136,3162709,3162242,3162242,3162988,3162709,3162709,3162136,3162242,3162242,3162709,3162988,3162136,3162988,3162988,3162242,3162136,3162988,3162136,3162136,3162242,3162988,3162988,3162144,3162673,3162988,3162144,3162673,3162988,3162988,3162144,3162673,3162144,3162673,3162144,3162673,3162144,3162144,3162673,3162144,3162673</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L2 W12/25; N=98; EHP=4414.775238; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x11,heavy:88x9,medium:83x7,medium:123x7,normal:17x12,normal:18x13,swarm:84x15 | manual: L1-scaled</t>
+          <t>L2 W12/25; N=318; EHP=182718.123094; air:25; ground:293 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1515,18 +1515,18 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164136,3164099,3164242,3164099,3164988,3164709,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164115,3164242,3164115,3164988,3164136,3164115,3164242,3164115,3164988,3164136,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164673,3164673</t>
+          <t>3164136,3164019,3164242,3164019,3164668,3164709,3164709,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164019,3164242,3164019,3164668,3164668,3164709,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164136,3164091,3164242,3164091,3164668,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164709,3164136,3164099,3164242,3164099,3164668,3164709,3164136,3164099,3164242,3164099,3164988,3164988,3164709,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164136,3164107,3164242,3164107,3164988,3164709,3164136,3164115,3164242,3164115,3164988,3164136,3164136,3164115,3164242,3164115,3164988,3164136,3164673,3164988,3164144,3164673,3164673,3164988,3164144,3164673,3164988,3164144,3164673,3164144,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164673,3164673,3164673,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164136,3164019,3164242,3164019,3164668,3164709,3164136,3164242,3164242,3164242,3164709,3164668,3164709,3164136,3164136,3164242,3164988,3164988,3164668,3164709,3164136,3164144,3164242,3164988,3164668,3164668,3164709,3164136,3164144,3164242,3164144,3164668,3164668,3164709,3164136,3164144,3164242,3164144,3164668,3164709,3164709,3164136,3164144,3164242,3164144,3164988,3164709,3164136,3164136,3164144,3164242,3164144,3164988,3164709,3164136,3164673,3164673,3164242,3164242,3164988,3164709,3164136,3164242,3164242,3164242,3164709,3164988,3164136,3164668,3164242,3164136,3164136,3164988,3164136,3164673,3164988,3164144,3164673,3164988,3164988,3164144,3164673,3164988,3164144,3164673,3164144,3164673,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164144,3164673,3164144,3164673,3164144,3164673,3164673,3164673,3164673,3164673,3164136,3164144,3164242,3164988,3164668,3164668,3164709,3164136,3164144,3164242,3164144,3164668,3164709,3164709,3164136,3164144,3164242,3164144,3164668,3164709,3164136,3164136,3164144,3164242,3164144,3164668,3164709,3164136,3164144,3164144,3164242,3164144,3164668,3164709,3164136,3164673,3164673,3164242,3164242,3164668,3164709,3164136,3164242,3164242,3164242,3164709,3164668,3164709,3164136,3164709,3164242,3164242,3164242,3164988,3164709,3164136,3164242,3164242,3164709,3164988,3164988,3164709,3164136,3164709,3164242,3164242,3164988,3164988,3164709,3164136,3164242,3164242,3164709,3164988,3164136,3164136,3164988,3164242,3164136,3164988,3164136,3164673,3164988,3164988,3164144,3164673,3164988,3164144,3164673,3164988,3164988,3164144,3164673,3164144,3164673,3164144,3164673,3164144,3164144,3164673,3164144,3164673</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L2 W13/25; N=104; EHP=5382.597937; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x12,heavy:88x10,medium:83x7,medium:123x8,normal:17x13,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
+          <t>L2 W13/25; N=337; EHP=220285.414372; air:28; ground:309 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1536,18 +1536,18 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166099,3166242,3166099,3166668,3166709,3166136,3166099,3166242,3166099,3166668,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166115,3166242,3166115,3166988,3166136,3166115,3166242,3166115,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166673,3166673,3166673</t>
+          <t>3166136,3166019,3166242,3166019,3166668,3166709,3166709,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166242,3166019,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166136,3166091,3166242,3166091,3166668,3166709,3166136,3166091,3166242,3166091,3166668,3166709,3166709,3166136,3166099,3166242,3166099,3166668,3166709,3166136,3166099,3166242,3166242,3166099,3166668,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166136,3166107,3166242,3166107,3166988,3166709,3166136,3166107,3166242,3166107,3166988,3166709,3166709,3166136,3166115,3166242,3166115,3166988,3166136,3166115,3166242,3166115,3166988,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166144,3166673,3166988,3166144,3166673,3166144,3166673,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166673,3166144,3166673,3166144,3166673,3166673,3166673,3166673,3166673,3166136,3166019,3166242,3166019,3166668,3166709,3166136,3166019,3166242,3166242,3166019,3166668,3166709,3166136,3166709,3166242,3166242,3166668,3166668,3166709,3166136,3166242,3166242,3166136,3166668,3166668,3166709,3166136,3166673,3166242,3166144,3166668,3166709,3166709,3166136,3166673,3166242,3166144,3166668,3166709,3166709,3166136,3166144,3166242,3166144,3166668,3166709,3166136,3166136,3166144,3166242,3166144,3166668,3166709,3166136,3166144,3166144,3166242,3166144,3166988,3166709,3166136,3166673,3166673,3166242,3166673,3166988,3166709,3166136,3166709,3166242,3166242,3166242,3166988,3166709,3166136,3166242,3166242,3166709,3166709,3166988,3166136,3166668,3166242,3166136,3166988,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166144,3166673,3166988,3166144,3166673,3166144,3166673,3166144,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166673,3166673,3166144,3166673,3166144,3166673,3166673,3166673,3166673,3166673,3166136,3166144,3166242,3166988,3166668,3166709,3166709,3166136,3166144,3166242,3166144,3166668,3166709,3166136,3166136,3166144,3166242,3166144,3166668,3166709,3166136,3166136,3166144,3166242,3166144,3166668,3166709,3166136,3166144,3166144,3166242,3166144,3166668,3166709,3166136,3166673,3166242,3166242,3166242,3166668,3166709,3166136,3166242,3166242,3166242,3166709,3166668,3166709,3166136,3166709,3166242,3166242,3166242,3166668,3166709,3166136,3166242,3166242,3166709,3166709,3166988,3166709,3166136,3166709,3166242,3166242,3166988,3166988,3166709,3166136,3166242,3166242,3166709,3166988,3166709,3166709,3166136,3166709,3166242,3166242,3166988,3166136,3166136,3166136,3166242,3166988,3166988,3166144,3166673,3166988,3166988,3166144,3166673,3166988,3166144,3166673,3166988,3166144,3166144,3166673,3166144,3166673,3166144,3166673,3166144,3166144,3166673,3166144,3166673</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>240</v>
+        <v>397</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L2 W14/25; N=110; EHP=6501.228076; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x13,heavy:88x11,medium:83x8,medium:123x8,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
+          <t>L2 W14/25; N=358; EHP=267818.190261; air:30; ground:328 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1557,18 +1557,18 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168099,3168242,3168099,3168668,3168709,3168136,3168099,3168242,3168099,3168868,3168709,3168136,3168099,3168242,3168099,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168115,3168242,3168115,3168868,3168136,3168115,3168242,3168115,3168988,3168136,3168115,3168115,3168988,3168136,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168673,3168673</t>
+          <t>3168136,3168019,3168242,3168019,3168668,3168709,3168709,3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168091,3168242,3168242,3168091,3168668,3168709,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168136,3168091,3168242,3168091,3168668,3168709,3168136,3168099,3168242,3168099,3168668,3168709,3168709,3168136,3168099,3168242,3168099,3168868,3168709,3168136,3168099,3168242,3168242,3168099,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168136,3168107,3168242,3168107,3168868,3168709,3168136,3168107,3168242,3168107,3168868,3168709,3168709,3168136,3168115,3168242,3168115,3168868,3168136,3168115,3168242,3168115,3168988,3168988,3168136,3168115,3168115,3168988,3168136,3168673,3168988,3168144,3168673,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168144,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168144,3168673,3168673,3168673,3168673,3168136,3168019,3168242,3168242,3168019,3168668,3168709,3168136,3168019,3168242,3168019,3168668,3168709,3168136,3168136,3168091,3168242,3168709,3168668,3168709,3168136,3168136,3168136,3168242,3168988,3168668,3168709,3168136,3168673,3168242,3168242,3168144,3168668,3168709,3168136,3168673,3168242,3168144,3168144,3168668,3168709,3168136,3168144,3168242,3168144,3168144,3168868,3168709,3168136,3168144,3168242,3168144,3168868,3168868,3168709,3168136,3168144,3168242,3168144,3168868,3168709,3168709,3168136,3168144,3168242,3168673,3168868,3168709,3168709,3168136,3168242,3168242,3168709,3168868,3168709,3168136,3168136,3168709,3168242,3168242,3168868,3168136,3168136,3168242,3168242,3168668,3168988,3168136,3168242,3168668,3168988,3168988,3168136,3168673,3168988,3168144,3168673,3168988,3168144,3168144,3168673,3168988,3168144,3168673,3168144,3168673,3168144,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168144,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168673,3168673,3168673,3168136,3168988,3168242,3168673,3168673,3168668,3168709,3168136,3168144,3168242,3168144,3168668,3168668,3168709,3168136,3168144,3168242,3168144,3168668,3168668,3168709,3168136,3168144,3168242,3168144,3168668,3168709,3168709,3168136,3168144,3168242,3168144,3168668,3168709,3168136,3168136,3168673,3168242,3168242,3168668,3168709,3168136,3168136,3168242,3168242,3168709,3168868,3168709,3168136,3168709,3168709,3168242,3168242,3168868,3168709,3168136,3168242,3168242,3168242,3168709,3168868,3168709,3168136,3168709,3168242,3168242,3168242,3168868,3168709,3168136,3168242,3168242,3168709,3168709,3168868,3168709,3168136,3168709,3168242,3168242,3168868,3168868,3168136,3168136,3168242,3168868,3168988,3168136,3168136,3168242,3168868,3168988,3168136,3168673,3168988,3168144,3168144,3168673,3168988,3168144,3168673,3168988,3168144,3168673,3168673,3168144,3168673,3168144,3168673,3168144,3168673,3168673,3168144,3168673,3168144</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>195</v>
+        <v>393</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L2 W15/25; N=116; EHP=11349.009383; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x13,heavy:88x11,medium:83x6,medium:108x6,medium:123x5,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
+          <t>L2 W15/25; N=377; EHP=365029.735965; air:33; ground:344 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1578,18 +1578,18 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170115,3170242,3170115,3170988,3170136,3170115,3170242,3170115,3170988,3170144,3170115,3170115,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170673,3170673,3170673,3170673</t>
+          <t>3170136,3170019,3170242,3170019,3170668,3170709,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170242,3170019,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170136,3170091,3170242,3170091,3170668,3170709,3170136,3170091,3170242,3170091,3170668,3170709,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170242,3170099,3170868,3170709,3170136,3170099,3170242,3170099,3170868,3170709,3170136,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170709,3170136,3170107,3170242,3170107,3170868,3170709,3170136,3170115,3170242,3170242,3170115,3170988,3170136,3170115,3170242,3170115,3170988,3170144,3170115,3170115,3170988,3170144,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170673,3170988,3170144,3170673,3170144,3170673,3170144,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170144,3170673,3170144,3170673,3170673,3170673,3170673,3170673,3170673,3170673,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170136,3170019,3170242,3170019,3170668,3170709,3170136,3170019,3170242,3170019,3170668,3170709,3170709,3170136,3170242,3170242,3170136,3170668,3170709,3170709,3170136,3170988,3170242,3170673,3170668,3170709,3170136,3170136,3170988,3170242,3170673,3170668,3170709,3170136,3170144,3170144,3170242,3170144,3170868,3170709,3170136,3170144,3170144,3170242,3170144,3170868,3170709,3170136,3170144,3170242,3170242,3170144,3170868,3170709,3170136,3170144,3170242,3170673,3170673,3170868,3170709,3170136,3170673,3170242,3170242,3170242,3170868,3170709,3170136,3170242,3170242,3170709,3170868,3170868,3170709,3170136,3170709,3170242,3170242,3170988,3170136,3170136,3170136,3170242,3170668,3170988,3170144,3170242,3170242,3170668,3170988,3170144,3170673,3170988,3170144,3170673,3170673,3170988,3170144,3170673,3170988,3170144,3170673,3170144,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170144,3170673,3170144,3170673,3170144,3170673,3170673,3170673,3170673,3170673,3170673,3170673,3170136,3170988,3170988,3170242,3170673,3170668,3170709,3170136,3170144,3170242,3170242,3170144,3170668,3170709,3170136,3170144,3170242,3170144,3170144,3170668,3170709,3170136,3170144,3170242,3170144,3170144,3170668,3170709,3170136,3170144,3170242,3170673,3170668,3170668,3170709,3170136,3170673,3170242,3170242,3170668,3170709,3170709,3170136,3170242,3170242,3170709,3170868,3170709,3170709,3170136,3170709,3170242,3170242,3170868,3170709,3170136,3170136,3170242,3170242,3170709,3170868,3170709,3170136,3170709,3170709,3170242,3170242,3170868,3170709,3170136,3170242,3170242,3170242,3170709,3170868,3170709,3170136,3170709,3170242,3170242,3170242,3170868,3170709,3170136,3170242,3170242,3170709,3170709,3170988,3170136,3170868,3170242,3170136,3170988,3170988,3170144,3170136,3170242,3170988,3170144,3170673,3170988,3170988,3170144,3170673,3170988,3170144,3170673,3170988,3170144,3170144,3170673,3170144,3170673,3170144,3170673,3170144,3170144,3170673,3170144,3170673</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L2 W16/25; N=122; EHP=11579.277913; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x14,heavy:88x12,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
+          <t>L2 W16/25; N=396; EHP=412947.441049; air:36; ground:360 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1599,18 +1599,18 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172115,3172242,3172115,3172988,3172136,3172115,3172242,3172115,3172988,3172136,3172115,3172242,3172115,3172988,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172673,3172673</t>
+          <t>3172136,3172019,3172242,3172019,3172668,3172709,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172091,3172668,3172709,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172868,3172709,3172136,3172099,3172242,3172099,3172868,3172709,3172136,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172709,3172136,3172107,3172242,3172107,3172868,3172709,3172136,3172115,3172242,3172115,3172988,3172988,3172136,3172115,3172242,3172115,3172988,3172136,3172115,3172242,3172115,3172988,3172988,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172144,3172673,3172144,3172673,3172673,3172673,3172673,3172673,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172242,3172019,3172668,3172709,3172136,3172019,3172242,3172019,3172668,3172709,3172136,3172136,3172091,3172242,3172091,3172668,3172709,3172136,3172091,3172242,3172136,3172136,3172668,3172709,3172136,3172673,3172242,3172144,3172668,3172668,3172709,3172136,3172673,3172242,3172144,3172868,3172709,3172709,3172136,3172144,3172242,3172144,3172868,3172709,3172709,3172136,3172144,3172242,3172144,3172868,3172709,3172136,3172136,3172144,3172242,3172144,3172868,3172709,3172136,3172144,3172144,3172242,3172144,3172868,3172709,3172136,3172673,3172673,3172242,3172242,3172868,3172709,3172136,3172242,3172242,3172242,3172709,3172988,3172136,3172668,3172242,3172136,3172988,3172988,3172136,3172709,3172242,3172242,3172988,3172136,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172673,3172988,3172144,3172673,3172988,3172144,3172673,3172144,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172144,3172673,3172144,3172673,3172673,3172673,3172673,3172673,3172136,3172673,3172242,3172144,3172668,3172709,3172136,3172136,3172673,3172242,3172144,3172668,3172709,3172136,3172144,3172144,3172242,3172144,3172668,3172709,3172136,3172144,3172144,3172242,3172144,3172668,3172709,3172136,3172144,3172242,3172242,3172144,3172668,3172709,3172136,3172144,3172242,3172144,3172144,3172668,3172709,3172136,3172673,3172242,3172242,3172242,3172868,3172709,3172136,3172242,3172242,3172709,3172868,3172868,3172709,3172136,3172709,3172242,3172242,3172868,3172709,3172709,3172136,3172242,3172242,3172709,3172868,3172709,3172709,3172136,3172709,3172242,3172242,3172868,3172709,3172136,3172136,3172242,3172242,3172709,3172868,3172709,3172136,3172709,3172709,3172242,3172242,3172988,3172136,3172136,3172242,3172242,3172868,3172988,3172136,3172242,3172242,3172709,3172988,3172988,3172136,3172673,3172988,3172144,3172673,3172988,3172144,3172144,3172673,3172988,3172144,3172673,3172988,3172144,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673,3172673,3172144,3172673,3172144</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L2 W17/25; N=128; EHP=11805.770179; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x15,heavy:88x12,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
+          <t>L2 W17/25; N=415; EHP=421328.419959; air:39; ground:376 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1620,18 +1620,18 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174099,3174242,3174099,3174668,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174115,3174242,3174115,3174868,3174136,3174115,3174242,3174115,3174988,3174136,3174115,3174242,3174115,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174673,3174673,3174673,3174673</t>
+          <t>3174136,3174019,3174242,3174019,3174668,3174709,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174136,3174091,3174242,3174091,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174709,3174136,3174099,3174242,3174099,3174668,3174709,3174136,3174099,3174242,3174099,3174868,3174868,3174709,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174136,3174099,3174242,3174099,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174709,3174136,3174107,3174242,3174107,3174868,3174709,3174136,3174107,3174242,3174107,3174868,3174868,3174709,3174136,3174115,3174242,3174115,3174868,3174136,3174115,3174242,3174115,3174988,3174988,3174136,3174115,3174242,3174115,3174988,3174144,3174673,3174988,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174144,3174673,3174988,3174144,3174673,3174144,3174673,3174144,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174673,3174673,3174673,3174673,3174673,3174136,3174019,3174242,3174019,3174668,3174668,3174709,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174136,3174019,3174242,3174019,3174668,3174709,3174136,3174091,3174242,3174091,3174668,3174709,3174709,3174136,3174091,3174242,3174242,3174668,3174709,3174136,3174988,3174988,3174242,3174673,3174668,3174709,3174136,3174988,3174242,3174242,3174673,3174668,3174709,3174136,3174144,3174242,3174242,3174144,3174868,3174709,3174136,3174144,3174242,3174144,3174144,3174868,3174709,3174136,3174144,3174242,3174144,3174868,3174868,3174709,3174136,3174144,3174242,3174144,3174868,3174709,3174709,3174136,3174673,3174242,3174673,3174868,3174709,3174709,3174136,3174709,3174242,3174242,3174868,3174709,3174136,3174136,3174242,3174242,3174709,3174868,3174136,3174668,3174242,3174242,3174136,3174988,3174136,3174709,3174242,3174242,3174242,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174144,3174673,3174144,3174673,3174673,3174673,3174673,3174673,3174673,3174673,3174136,3174673,3174242,3174144,3174668,3174709,3174709,3174136,3174673,3174242,3174144,3174668,3174709,3174709,3174136,3174144,3174242,3174144,3174668,3174709,3174136,3174136,3174144,3174242,3174144,3174668,3174709,3174136,3174144,3174144,3174242,3174144,3174668,3174709,3174136,3174144,3174144,3174242,3174673,3174668,3174709,3174136,3174673,3174242,3174242,3174242,3174668,3174709,3174136,3174242,3174242,3174709,3174709,3174868,3174709,3174136,3174709,3174242,3174242,3174868,3174868,3174709,3174136,3174242,3174242,3174709,3174868,3174868,3174709,3174136,3174709,3174242,3174242,3174868,3174709,3174709,3174136,3174242,3174242,3174709,3174868,3174709,3174136,3174136,3174709,3174242,3174242,3174868,3174709,3174136,3174242,3174242,3174242,3174709,3174868,3174136,3174868,3174242,3174242,3174136,3174988,3174136,3174709,3174242,3174242,3174988,3174988,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174144,3174673,3174988,3174144,3174673,3174988,3174144,3174144,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174673,3174144,3174673,3174144</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L2 W18/25; N=134; EHP=12620.575360; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x16,heavy:88x13,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
+          <t>L2 W18/25; N=435; EHP=452642.905043; air:41; ground:394 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1641,18 +1641,18 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176115,3176242,3176115,3176988,3176136,3176115,3176242,3176115,3176988,3176136,3176115,3176115,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176673,3176673,3176673,3176673,3176673</t>
+          <t>3176136,3176019,3176242,3176019,3176668,3176709,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176709,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176099,3176242,3176242,3176099,3176868,3176709,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176136,3176099,3176242,3176099,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176242,3176107,3176868,3176709,3176136,3176107,3176242,3176107,3176868,3176709,3176136,3176136,3176115,3176242,3176115,3176988,3176136,3176115,3176242,3176115,3176988,3176136,3176136,3176115,3176115,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176144,3176673,3176144,3176673,3176673,3176673,3176673,3176673,3176673,3176673,3176673,3176136,3176019,3176242,3176019,3176668,3176709,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176242,3176019,3176668,3176709,3176136,3176019,3176242,3176019,3176668,3176709,3176136,3176136,3176091,3176242,3176091,3176668,3176709,3176136,3176673,3176242,3176242,3176144,3176668,3176709,3176136,3176673,3176242,3176144,3176144,3176668,3176709,3176136,3176673,3176242,3176673,3176868,3176868,3176709,3176136,3176673,3176242,3176673,3176868,3176868,3176709,3176136,3176673,3176242,3176673,3176868,3176709,3176709,3176136,3176673,3176242,3176673,3176868,3176709,3176709,3176136,3176673,3176242,3176673,3176868,3176709,3176136,3176136,3176242,3176242,3176709,3176868,3176709,3176136,3176709,3176709,3176242,3176242,3176868,3176709,3176136,3176242,3176242,3176242,3176709,3176988,3176136,3176668,3176242,3176136,3176136,3176988,3176136,3176709,3176136,3176988,3176144,3176673,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176144,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176144,3176144,3176673,3176673,3176673,3176673,3176673,3176673,3176673,3176673,3176136,3176988,3176242,3176673,3176668,3176709,3176709,3176136,3176988,3176242,3176673,3176668,3176709,3176709,3176136,3176673,3176242,3176673,3176668,3176709,3176136,3176136,3176673,3176242,3176673,3176668,3176709,3176136,3176673,3176673,3176242,3176673,3176668,3176709,3176136,3176673,3176673,3176242,3176673,3176668,3176709,3176136,3176673,3176242,3176242,3176242,3176668,3176709,3176136,3176242,3176242,3176242,3176709,3176868,3176709,3176136,3176709,3176242,3176242,3176242,3176868,3176709,3176136,3176242,3176242,3176709,3176868,3176868,3176709,3176136,3176709,3176242,3176242,3176868,3176868,3176709,3176136,3176242,3176242,3176709,3176868,3176709,3176709,3176136,3176709,3176242,3176242,3176868,3176709,3176136,3176136,3176242,3176242,3176709,3176868,3176709,3176136,3176136,3176709,3176242,3176242,3176988,3176136,3176136,3176242,3176242,3176868,3176988,3176136,3176242,3176988,3176988,3176988,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176144,3176673,3176988,3176144,3176673,3176988,3176144,3176673,3176673,3176144,3176673,3176144,3176673,3176144,3176673,3176673,3176144,3176673,3176144</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>230</v>
+        <v>394</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L2 W19/25; N=140; EHP=14617.416655; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x16,heavy:88x14,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
+          <t>L2 W19/25; N=455; EHP=519869.065404; air:44; ground:411 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
@@ -1662,18 +1662,18 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178115,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178673,3178673,3178673</t>
+          <t>3178136,3178019,3178242,3178019,3178668,3178709,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178242,3178019,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178099,3178242,3178242,3178099,3178868,3178709,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178136,3178099,3178242,3178099,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178242,3178107,3178868,3178709,3178136,3178107,3178242,3178107,3178868,3178709,3178136,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178242,3178115,3178988,3178136,3178136,3178115,3178242,3178115,3178988,3178136,3178115,3178115,3178988,3178144,3178673,3178988,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178673,3178673,3178673,3178673,3178673,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178242,3178019,3178668,3178709,3178136,3178019,3178242,3178019,3178668,3178709,3178136,3178136,3178091,3178242,3178091,3178668,3178709,3178136,3178091,3178242,3178091,3178668,3178709,3178709,3178136,3178091,3178242,3178988,3178668,3178709,3178136,3178136,3178144,3178242,3178988,3178668,3178709,3178136,3178673,3178673,3178242,3178673,3178868,3178709,3178136,3178673,3178242,3178242,3178673,3178868,3178709,3178136,3178673,3178242,3178242,3178673,3178868,3178709,3178136,3178673,3178242,3178673,3178673,3178868,3178709,3178136,3178673,3178242,3178673,3178673,3178868,3178709,3178136,3178673,3178242,3178242,3178868,3178868,3178709,3178136,3178242,3178242,3178709,3178868,3178709,3178709,3178136,3178709,3178242,3178242,3178988,3178136,3178136,3178136,3178242,3178668,3178988,3178136,3178242,3178242,3178242,3178709,3178988,3178136,3178668,3178709,3178988,3178144,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178144,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178673,3178673,3178673,3178673,3178673,3178136,3178144,3178242,3178988,3178988,3178668,3178709,3178136,3178673,3178242,3178673,3178668,3178668,3178709,3178136,3178673,3178242,3178673,3178668,3178668,3178709,3178136,3178673,3178242,3178673,3178668,3178709,3178709,3178136,3178673,3178242,3178673,3178668,3178709,3178709,3178136,3178673,3178242,3178673,3178668,3178709,3178136,3178136,3178673,3178242,3178242,3178668,3178709,3178136,3178242,3178242,3178242,3178709,3178868,3178709,3178136,3178709,3178709,3178242,3178242,3178868,3178709,3178136,3178242,3178242,3178242,3178709,3178868,3178709,3178136,3178709,3178242,3178242,3178242,3178868,3178709,3178136,3178242,3178242,3178709,3178709,3178868,3178709,3178136,3178709,3178242,3178242,3178868,3178868,3178709,3178136,3178242,3178242,3178709,3178868,3178868,3178709,3178136,3178709,3178242,3178242,3178988,3178136,3178136,3178136,3178242,3178868,3178988,3178136,3178242,3178242,3178242,3178136,3178988,3178136,3178136,3178242,3178988,3178988,3178144,3178673,3178988,3178144,3178673,3178988,3178144,3178144,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673,3178144,3178673,3178144,3178144,3178673,3178144,3178673</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>185</v>
+        <v>388</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L2 W20/25; N=146; EHP=24562.981882; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x17,heavy:88x14,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
+          <t>L2 W20/25; N=474; EHP=608698.376869; air:47; ground:427 | l02-redesign-20261101 | ground+50-hp+50-gold+15-20261101 | ground15-iv-keepwindow-20261101</t>
         </is>
       </c>
     </row>
